--- a/etf_holdings/2026-09-09_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-09_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -494,29 +494,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00985A(49,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00403A(-100,000)</t>
+          <t>00991A(-100,000)、00985A(-17,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>欣興電子</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -524,29 +524,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00405A(150,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00991A(-100,000)、00985A(-17,000)</t>
+          <t>00985A(-54,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>欣興電子</t>
+          <t>弘塑</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -559,24 +559,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00405A(150,000)</t>
+          <t>00407A(新納入)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00985A(-54,000)</t>
+          <t>00405A(-20,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>弘塑</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -589,40 +589,10 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00407A(新納入)</t>
+          <t>00407A(40,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
-        <is>
-          <t>00405A(-20,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>00407A(40,000)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
         <is>
           <t>00985A(-17,000)</t>
         </is>

--- a/etf_holdings/2026-09-09_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-09_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -494,29 +494,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(49,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00991A(-100,000)、00985A(-17,000)</t>
+          <t>00403A(-100,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>欣興電子</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -524,29 +524,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00405A(150,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00985A(-54,000)</t>
+          <t>00991A(-100,000)、00985A(-17,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>弘塑</t>
+          <t>欣興電子</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -559,24 +559,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00407A(新納入)</t>
+          <t>00405A(150,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00405A(-20,000)</t>
+          <t>00985A(-54,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>弘塑</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -589,10 +589,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>00407A(新納入)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>00405A(-20,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>00407A(40,000)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>00985A(-17,000)</t>
         </is>
